--- a/data/dividends_info_20260517.xlsx
+++ b/data/dividends_info_20260517.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K183"/>
+  <dimension ref="A1:K163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3828,11 +3828,11 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7</v>
+        <v>0.24</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -3856,14 +3856,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>IT0001347308</t>
+          <t>IT0004967292</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>44.79999923706055</v>
+        <v>9.064999580383301</v>
       </c>
       <c r="I73" t="n">
-        <v>1.562500026609217</v>
+        <v>2.647545627242621</v>
       </c>
       <c r="J73" t="n">
         <v>1</v>
@@ -3875,11 +3875,11 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2.2</v>
+        <v>0.79</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -3898,19 +3898,19 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>IT0001031084</t>
+          <t>IT0000072170</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>56.34999847412109</v>
+        <v>21.34000015258789</v>
       </c>
       <c r="I74" t="n">
-        <v>3.904170469517149</v>
+        <v>3.701968108487558</v>
       </c>
       <c r="J74" t="n">
         <v>1</v>
@@ -3922,11 +3922,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.86</v>
+        <v>0.093</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -3950,14 +3950,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>IT0005508921</t>
+          <t>IT0005345233</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>9.371000289916992</v>
+        <v>5.28000020980835</v>
       </c>
       <c r="I75" t="n">
-        <v>9.177248675633301</v>
+        <v>1.761363566373337</v>
       </c>
       <c r="J75" t="n">
         <v>1</v>
@@ -3969,11 +3969,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -3992,19 +3992,19 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>IT0000066123</t>
+          <t>IT0005359101</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>12.21199989318848</v>
+        <v>6.599999904632568</v>
       </c>
       <c r="I76" t="n">
-        <v>4.585653495725568</v>
+        <v>0.909090922226919</v>
       </c>
       <c r="J76" t="n">
         <v>1</v>
@@ -4016,11 +4016,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.04</v>
+        <v>0.35</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -4044,14 +4044,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>IT0001472171</t>
+          <t>IT0001078911</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>2.160000085830688</v>
+        <v>33.72000122070312</v>
       </c>
       <c r="I77" t="n">
-        <v>1.851851778265873</v>
+        <v>1.037959630277563</v>
       </c>
       <c r="J77" t="n">
         <v>1</v>
@@ -4063,11 +4063,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.3</v>
+        <v>0.5543</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -4091,14 +4091,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>IT0003127930</t>
+          <t>IT0005090300</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>9.180000305175781</v>
+        <v>7.025000095367432</v>
       </c>
       <c r="I78" t="n">
-        <v>3.267973747570104</v>
+        <v>7.890391351959238</v>
       </c>
       <c r="J78" t="n">
         <v>1</v>
@@ -4110,11 +4110,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.108</v>
+        <v>0.06</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -4138,14 +4138,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>IT0005244618</t>
+          <t>IT0001077780</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>2.233386993408203</v>
+        <v>2.259999990463257</v>
       </c>
       <c r="I79" t="n">
-        <v>4.835704708532818</v>
+        <v>2.654867267840171</v>
       </c>
       <c r="J79" t="n">
         <v>1</v>
@@ -4157,11 +4157,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2.06</v>
+        <v>0.2</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -4185,14 +4185,14 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>IT0001128047</t>
+          <t>IT0003411417</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>98</v>
+        <v>12.80000019073486</v>
       </c>
       <c r="I80" t="n">
-        <v>2.102040816326531</v>
+        <v>1.562499976716936</v>
       </c>
       <c r="J80" t="n">
         <v>1</v>
@@ -4204,11 +4204,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.75</v>
+        <v>0.103</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -4232,14 +4232,14 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>IT0003121677</t>
+          <t>IT0005186371</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>15.56999969482422</v>
+        <v>6.934999942779541</v>
       </c>
       <c r="I81" t="n">
-        <v>4.81695577842121</v>
+        <v>1.485219911317226</v>
       </c>
       <c r="J81" t="n">
         <v>1</v>
@@ -4251,11 +4251,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.3</v>
+        <v>0.19</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -4279,14 +4279,14 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>NL0013995087</t>
+          <t>IT0000072618</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>14.10999965667725</v>
+        <v>5.735000133514404</v>
       </c>
       <c r="I82" t="n">
-        <v>2.126151717218729</v>
+        <v>3.312990332636106</v>
       </c>
       <c r="J82" t="n">
         <v>1</v>
@@ -4298,11 +4298,11 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.85</v>
+        <v>0.432</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -4326,14 +4326,14 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>IT0005246191</t>
+          <t>IT0005211237</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>53.59999847412109</v>
+        <v>10.13000011444092</v>
       </c>
       <c r="I83" t="n">
-        <v>1.585820940667364</v>
+        <v>4.264560662582404</v>
       </c>
       <c r="J83" t="n">
         <v>1</v>
@@ -4345,11 +4345,11 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.85</v>
+        <v>0.44</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -4373,14 +4373,14 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>IT0003115950</t>
+          <t>IT0005541336</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>36.7400016784668</v>
+        <v>26</v>
       </c>
       <c r="I84" t="n">
-        <v>2.313554603069554</v>
+        <v>1.692307692307692</v>
       </c>
       <c r="J84" t="n">
         <v>1</v>
@@ -4392,11 +4392,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1.3</v>
+        <v>0.03</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -4420,14 +4420,14 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>IT0003492391</t>
+          <t>IT0004522162</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>70.45999908447266</v>
+        <v>1</v>
       </c>
       <c r="I85" t="n">
-        <v>1.845018474157889</v>
+        <v>3</v>
       </c>
       <c r="J85" t="n">
         <v>1</v>
@@ -4439,11 +4439,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -4467,14 +4467,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>IT0001463063</t>
+          <t>IT0003428445</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>7.960000038146973</v>
+        <v>8.210000038146973</v>
       </c>
       <c r="I86" t="n">
-        <v>7.53768840608794</v>
+        <v>5.72472591737138</v>
       </c>
       <c r="J86" t="n">
         <v>1</v>
@@ -4486,11 +4486,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.47</v>
+        <v>1.4</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -4514,14 +4514,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>IT0005669558</t>
+          <t>IT0004965148</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>6.349999904632568</v>
+        <v>49.70999908447266</v>
       </c>
       <c r="I87" t="n">
-        <v>7.401574914310108</v>
+        <v>2.816334793370177</v>
       </c>
       <c r="J87" t="n">
         <v>1</v>
@@ -4533,11 +4533,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -4556,19 +4556,19 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>IT0005312027</t>
+          <t>IT0005366767</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>5.849999904632568</v>
+        <v>3.697000026702881</v>
       </c>
       <c r="I88" t="n">
-        <v>3.418803474537181</v>
+        <v>8.114687525916816</v>
       </c>
       <c r="J88" t="n">
         <v>1</v>
@@ -4580,11 +4580,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>0.12</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -4608,14 +4608,14 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>IT0001157020</t>
+          <t>IT0005594418</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>23.3799991607666</v>
+        <v>13.10000038146973</v>
       </c>
       <c r="I89" t="n">
-        <v>4.277160119312901</v>
+        <v>0.9160305076764956</v>
       </c>
       <c r="J89" t="n">
         <v>1</v>
@@ -4627,11 +4627,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.215</v>
+        <v>0.17</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -4655,14 +4655,14 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>IT0004356751</t>
+          <t>IT0005453748</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>4.75</v>
+        <v>3.650000095367432</v>
       </c>
       <c r="I90" t="n">
-        <v>4.526315789473684</v>
+        <v>4.657534124882996</v>
       </c>
       <c r="J90" t="n">
         <v>1</v>
@@ -4674,11 +4674,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.27</v>
+        <v>0.7</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -4697,19 +4697,19 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>IT0003132476</t>
+          <t>IT0005373789</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>23.52000045776367</v>
+        <v>21.39999961853027</v>
       </c>
       <c r="I91" t="n">
-        <v>1.147959161331037</v>
+        <v>3.271028095691504</v>
       </c>
       <c r="J91" t="n">
         <v>1</v>
@@ -4721,11 +4721,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.2</v>
+        <v>0.035</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -4749,14 +4749,14 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>IT0005521247</t>
+          <t>IT0005378143</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>9.539999961853027</v>
+        <v>2.339999914169312</v>
       </c>
       <c r="I92" t="n">
-        <v>2.096436067083091</v>
+        <v>1.495726550589419</v>
       </c>
       <c r="J92" t="n">
         <v>1</v>
@@ -4768,11 +4768,11 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.24</v>
+        <v>0.33</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -4796,14 +4796,14 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>IT0004967292</t>
+          <t>IT0005054967</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>9.064999580383301</v>
+        <v>5.909999847412109</v>
       </c>
       <c r="I93" t="n">
-        <v>2.647545627242621</v>
+        <v>5.583756489342407</v>
       </c>
       <c r="J93" t="n">
         <v>1</v>
@@ -4815,11 +4815,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.79</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -4843,14 +4843,14 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>IT0000072170</t>
+          <t>IT0004931496</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>21.34000015258789</v>
+        <v>0.9959999918937683</v>
       </c>
       <c r="I94" t="n">
-        <v>3.701968108487558</v>
+        <v>7.028112506999507</v>
       </c>
       <c r="J94" t="n">
         <v>1</v>
@@ -4862,11 +4862,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.093</v>
+        <v>0.71</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>IT0005345233</t>
+          <t>IT0003828271</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>5.28000020980835</v>
+        <v>51.5</v>
       </c>
       <c r="I95" t="n">
-        <v>1.761363566373337</v>
+        <v>1.378640776699029</v>
       </c>
       <c r="J95" t="n">
         <v>1</v>
@@ -4909,11 +4909,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.06</v>
+        <v>1.35</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -4932,19 +4932,19 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>IT0005359101</t>
+          <t>IT0005282865</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>6.599999904632568</v>
+        <v>97.69999694824219</v>
       </c>
       <c r="I96" t="n">
-        <v>0.909090922226919</v>
+        <v>1.381781005290286</v>
       </c>
       <c r="J96" t="n">
         <v>1</v>
@@ -4956,11 +4956,11 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.35</v>
+        <v>0.08</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -4984,14 +4984,14 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>IT0001078911</t>
+          <t>IT0005543613</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>33.72000122070312</v>
+        <v>7.019999980926514</v>
       </c>
       <c r="I97" t="n">
-        <v>1.037959630277563</v>
+        <v>1.13960114269746</v>
       </c>
       <c r="J97" t="n">
         <v>1</v>
@@ -5003,11 +5003,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5543</v>
+        <v>3</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -5031,14 +5031,14 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>IT0005090300</t>
+          <t>IT0001017851</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>7.025000095367432</v>
+        <v>260</v>
       </c>
       <c r="I98" t="n">
-        <v>7.890391351959238</v>
+        <v>1.153846153846154</v>
       </c>
       <c r="J98" t="n">
         <v>1</v>
@@ -5050,11 +5050,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.06</v>
+        <v>0.17</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -5078,14 +5078,14 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>IT0001077780</t>
+          <t>IT0005495657</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>2.259999990463257</v>
+        <v>4.65500020980835</v>
       </c>
       <c r="I99" t="n">
-        <v>2.654867267840171</v>
+        <v>3.651986946032792</v>
       </c>
       <c r="J99" t="n">
         <v>1</v>
@@ -5097,11 +5097,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.2</v>
+        <v>0.297</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -5125,14 +5125,14 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>IT0003411417</t>
+          <t>IT0005568461</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>12.80000019073486</v>
+        <v>7.400000095367432</v>
       </c>
       <c r="I100" t="n">
-        <v>1.562499976716936</v>
+        <v>4.013513461789396</v>
       </c>
       <c r="J100" t="n">
         <v>1</v>
@@ -5144,11 +5144,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.103</v>
+        <v>0.45</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -5172,14 +5172,14 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>IT0005186371</t>
+          <t>IT0001206769</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>6.934999942779541</v>
+        <v>59.09999847412109</v>
       </c>
       <c r="I101" t="n">
-        <v>1.485219911317226</v>
+        <v>0.7614213394557828</v>
       </c>
       <c r="J101" t="n">
         <v>1</v>
@@ -5191,11 +5191,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.19</v>
+        <v>0.04</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -5219,14 +5219,14 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>IT0000072618</t>
+          <t>IT0005595423</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>5.735000133514404</v>
+        <v>5.099999904632568</v>
       </c>
       <c r="I102" t="n">
-        <v>3.312990332636106</v>
+        <v>0.784313740156468</v>
       </c>
       <c r="J102" t="n">
         <v>1</v>
@@ -5238,11 +5238,11 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.432</v>
+        <v>1.05</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -5266,14 +5266,14 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>IT0005211237</t>
+          <t>IT0003549422</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>10.13000011444092</v>
+        <v>38.54000091552734</v>
       </c>
       <c r="I103" t="n">
-        <v>4.264560662582404</v>
+        <v>2.724442073318599</v>
       </c>
       <c r="J103" t="n">
         <v>1</v>
@@ -5285,11 +5285,11 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.44</v>
+        <v>0.05</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -5313,14 +5313,14 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>IT0005541336</t>
+          <t>IT0005621070</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>26</v>
+        <v>1.5</v>
       </c>
       <c r="I104" t="n">
-        <v>1.692307692307692</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="J104" t="n">
         <v>1</v>
@@ -5332,11 +5332,11 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.03</v>
+        <v>0.38</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -5360,14 +5360,14 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>IT0004522162</t>
+          <t>IT0005162406</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>1</v>
+        <v>21.29999923706055</v>
       </c>
       <c r="I105" t="n">
-        <v>3</v>
+        <v>1.78403762258745</v>
       </c>
       <c r="J105" t="n">
         <v>1</v>
@@ -5379,15 +5379,15 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>TENARIS S.A.</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.47</v>
+        <v>0.6</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>EURO</t>
+          <t>DOLLARI USA</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5407,14 +5407,14 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>IT0003428445</t>
+          <t>LU2598331598</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>8.210000038146973</v>
+        <v>26.65999984741211</v>
       </c>
       <c r="I106" t="n">
-        <v>5.72472591737138</v>
+        <v>2.250562653541208</v>
       </c>
       <c r="J106" t="n">
         <v>1</v>
@@ -5426,11 +5426,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1.4</v>
+        <v>0.35</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -5454,14 +5454,14 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>IT0004965148</t>
+          <t>IT0001454435</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>49.70999908447266</v>
+        <v>37.09999847412109</v>
       </c>
       <c r="I107" t="n">
-        <v>2.816334793370177</v>
+        <v>0.9433962652158614</v>
       </c>
       <c r="J107" t="n">
         <v>1</v>
@@ -5473,11 +5473,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.3</v>
+        <v>0.017</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -5501,14 +5501,14 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>IT0005366767</t>
+          <t>IT0005658841</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>3.697000026702881</v>
+        <v>3.619999885559082</v>
       </c>
       <c r="I108" t="n">
-        <v>8.114687525916816</v>
+        <v>0.4696132745146338</v>
       </c>
       <c r="J108" t="n">
         <v>1</v>
@@ -5520,11 +5520,11 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.12</v>
+        <v>0.01</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -5548,14 +5548,14 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>IT0005594418</t>
+          <t>IT0005573065</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>13.10000038146973</v>
+        <v>2.815000057220459</v>
       </c>
       <c r="I109" t="n">
-        <v>0.9160305076764956</v>
+        <v>0.3552397796351747</v>
       </c>
       <c r="J109" t="n">
         <v>1</v>
@@ -5567,11 +5567,11 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.17</v>
+        <v>1.12</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -5595,14 +5595,14 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>IT0005453748</t>
+          <t>IT0004810054</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>3.650000095367432</v>
+        <v>22.14999961853027</v>
       </c>
       <c r="I110" t="n">
-        <v>4.657534124882996</v>
+        <v>5.05643349566033</v>
       </c>
       <c r="J110" t="n">
         <v>1</v>
@@ -5614,11 +5614,11 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -5642,14 +5642,14 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>IT0005373789</t>
+          <t>IT0004717200</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>21.39999961853027</v>
+        <v>1.559999942779541</v>
       </c>
       <c r="I111" t="n">
-        <v>3.271028095691504</v>
+        <v>6.410256645383224</v>
       </c>
       <c r="J111" t="n">
         <v>1</v>
@@ -5661,11 +5661,11 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.035</v>
+        <v>0.26</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -5689,14 +5689,14 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>IT0005378143</t>
+          <t>IT0003865570</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>2.339999914169312</v>
+        <v>2.589999914169312</v>
       </c>
       <c r="I112" t="n">
-        <v>1.495726550589419</v>
+        <v>10.03861037128218</v>
       </c>
       <c r="J112" t="n">
         <v>1</v>
@@ -5708,11 +5708,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.33</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -5736,14 +5736,14 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>IT0005054967</t>
+          <t>IT0005610958</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>5.909999847412109</v>
+        <v>2.200000047683716</v>
       </c>
       <c r="I113" t="n">
-        <v>5.583756489342407</v>
+        <v>4.195454454520519</v>
       </c>
       <c r="J113" t="n">
         <v>1</v>
@@ -5755,11 +5755,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5783,30 +5783,30 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>IT0004931496</t>
+          <t>IT0001006128</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>0.9959999918937683</v>
+        <v>8.600000381469727</v>
       </c>
       <c r="I114" t="n">
-        <v>7.028112506999507</v>
+        <v>4.069767261338023</v>
       </c>
       <c r="J114" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="K114" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.71</v>
+        <v>0.096</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -5815,12 +5815,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5830,30 +5830,30 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>IT0003828271</t>
+          <t>IT0005543332</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>51.5</v>
+        <v>5.199999809265137</v>
       </c>
       <c r="I115" t="n">
-        <v>1.378640776699029</v>
+        <v>1.846153913870368</v>
       </c>
       <c r="J115" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="K115" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>1.35</v>
+        <v>0.3</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -5862,12 +5862,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5877,30 +5877,30 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>IT0005282865</t>
+          <t>IT0005416281</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>97.69999694824219</v>
+        <v>6.050000190734863</v>
       </c>
       <c r="I116" t="n">
-        <v>1.381781005290286</v>
+        <v>4.958677529621045</v>
       </c>
       <c r="J116" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="K116" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -5909,12 +5909,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5924,30 +5924,30 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>IT0005543613</t>
+          <t>IT0005037905</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>7.019999980926514</v>
+        <v>11.5</v>
       </c>
       <c r="I117" t="n">
-        <v>1.13960114269746</v>
+        <v>1.739130434782609</v>
       </c>
       <c r="J117" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="K117" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>3</v>
+        <v>0.06</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -5956,45 +5956,45 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>IT0001017851</t>
+          <t>IT0005337818</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>260</v>
+        <v>9.399999618530273</v>
       </c>
       <c r="I118" t="n">
-        <v>1.153846153846154</v>
+        <v>0.6382978982437579</v>
       </c>
       <c r="J118" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="K118" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.17</v>
+        <v>0.5</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -6018,30 +6018,30 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>IT0005495657</t>
+          <t>IT0005075764</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>4.65500020980835</v>
+        <v>18.81999969482422</v>
       </c>
       <c r="I119" t="n">
-        <v>3.651986946032792</v>
+        <v>2.656748183356812</v>
       </c>
       <c r="J119" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="K119" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.297</v>
+        <v>0.06</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -6050,12 +6050,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -6065,30 +6065,30 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>IT0005568461</t>
+          <t>IT0004376858</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>7.400000095367432</v>
+        <v>2.180000066757202</v>
       </c>
       <c r="I120" t="n">
-        <v>4.013513461789396</v>
+        <v>2.752293493699352</v>
       </c>
       <c r="J120" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="K120" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -6112,30 +6112,30 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>IT0001206769</t>
+          <t>IT0005138703</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>59.09999847412109</v>
+        <v>15.03999996185303</v>
       </c>
       <c r="I121" t="n">
-        <v>0.7614213394557828</v>
+        <v>3.324468093538457</v>
       </c>
       <c r="J121" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="K121" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -6144,12 +6144,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -6159,30 +6159,30 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>IT0005595423</t>
+          <t>IT0005430951</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>5.099999904632568</v>
+        <v>3.779999971389771</v>
       </c>
       <c r="I122" t="n">
-        <v>0.784313740156468</v>
+        <v>2.645502665526042</v>
       </c>
       <c r="J122" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="K122" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>1.05</v>
+        <v>0.11</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -6206,30 +6206,30 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>IT0003549422</t>
+          <t>IT0005339160</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>38.54000091552734</v>
+        <v>3.700000047683716</v>
       </c>
       <c r="I123" t="n">
-        <v>2.724442073318599</v>
+        <v>2.972972934658812</v>
       </c>
       <c r="J123" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="K123" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.05</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -6238,12 +6238,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -6253,30 +6253,30 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>IT0005621070</t>
+          <t>IT0005545238</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>1.5</v>
+        <v>8.899999618530273</v>
       </c>
       <c r="I124" t="n">
-        <v>3.333333333333333</v>
+        <v>0.9550562207106782</v>
       </c>
       <c r="J124" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="K124" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.38</v>
+        <v>0.095</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -6285,12 +6285,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6300,44 +6300,44 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>IT0005162406</t>
+          <t>IT0005466963</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>21.29999923706055</v>
+        <v>4.949999809265137</v>
       </c>
       <c r="I125" t="n">
-        <v>1.78403762258745</v>
+        <v>1.919191993142792</v>
       </c>
       <c r="J125" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="K125" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>TENARIS S.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.6</v>
+        <v>0.03</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>DOLLARI USA</t>
+          <t>EURO</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6347,30 +6347,30 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>LU2598331598</t>
+          <t>IT0005521551</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>26.65999984741211</v>
+        <v>1.139999985694885</v>
       </c>
       <c r="I126" t="n">
-        <v>2.250562653541208</v>
+        <v>2.631578980390385</v>
       </c>
       <c r="J126" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="K126" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.35</v>
+        <v>0.09</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -6379,12 +6379,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6394,30 +6394,30 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>IT0001454435</t>
+          <t>IT0005246142</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>37.09999847412109</v>
+        <v>7.849999904632568</v>
       </c>
       <c r="I127" t="n">
-        <v>0.9433962652158614</v>
+        <v>1.14649682921509</v>
       </c>
       <c r="J127" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="K127" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.017</v>
+        <v>0.1</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -6441,30 +6441,30 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>IT0005658841</t>
+          <t>IT0005532525</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>3.619999885559082</v>
+        <v>8.399999618530273</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4696132745146338</v>
+        <v>1.190476244539363</v>
       </c>
       <c r="J128" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="K128" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.01</v>
+        <v>0.22</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -6473,12 +6473,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -6488,30 +6488,30 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>IT0005573065</t>
+          <t>IT0004171440</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>2.815000057220459</v>
+        <v>6.96999979019165</v>
       </c>
       <c r="I129" t="n">
-        <v>0.3552397796351747</v>
+        <v>3.156384600033837</v>
       </c>
       <c r="J129" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="K129" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1.12</v>
+        <v>0.61</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -6520,12 +6520,12 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -6535,30 +6535,30 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>IT0004810054</t>
+          <t>IT0004720733</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>22.14999961853027</v>
+        <v>28.04999923706055</v>
       </c>
       <c r="I130" t="n">
-        <v>5.05643349566033</v>
+        <v>2.174688116190922</v>
       </c>
       <c r="J130" t="n">
-        <v>1</v>
+        <v>-13</v>
       </c>
       <c r="K130" t="n">
-        <v>3</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -6567,12 +6567,12 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6582,30 +6582,30 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>IT0004717200</t>
+          <t>IT0005386369</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>1.559999942779541</v>
+        <v>2.859999895095825</v>
       </c>
       <c r="I131" t="n">
-        <v>6.410256645383224</v>
+        <v>5.244755437131728</v>
       </c>
       <c r="J131" t="n">
-        <v>1</v>
+        <v>-13</v>
       </c>
       <c r="K131" t="n">
-        <v>3</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.26</v>
+        <v>0.7</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -6614,12 +6614,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6629,30 +6629,30 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>IT0003865588</t>
+          <t>IT0001268561</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>8.600000381469727</v>
+        <v>11.10000038146973</v>
       </c>
       <c r="I132" t="n">
-        <v>3.023255679851103</v>
+        <v>6.306306089579743</v>
       </c>
       <c r="J132" t="n">
-        <v>1</v>
+        <v>-13</v>
       </c>
       <c r="K132" t="n">
-        <v>3</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.5105</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -6661,12 +6661,12 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -6676,44 +6676,44 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>IT0005610958</t>
+          <t>IT0001041000</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>2.200000047683716</v>
+        <v>8.649999618530273</v>
       </c>
       <c r="I133" t="n">
-        <v>4.195454454520519</v>
+        <v>5.901734364315953</v>
       </c>
       <c r="J133" t="n">
-        <v>1</v>
+        <v>-13</v>
       </c>
       <c r="K133" t="n">
-        <v>3</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.35</v>
+        <v>0.27</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>EURO</t>
+          <t>DOLLARI USA</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6723,30 +6723,30 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>IT0001006128</t>
+          <t>LU2592315662</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>8.600000381469727</v>
+        <v>8.340000152587891</v>
       </c>
       <c r="I134" t="n">
-        <v>4.069767261338023</v>
+        <v>3.237410012711084</v>
       </c>
       <c r="J134" t="n">
-        <v>-6</v>
+        <v>-13</v>
       </c>
       <c r="K134" t="n">
-        <v>-4</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.096</v>
+        <v>0.35</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6770,30 +6770,30 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>IT0005543332</t>
+          <t>IT0003850929</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>5.199999809265137</v>
+        <v>7.045000076293945</v>
       </c>
       <c r="I135" t="n">
-        <v>1.846153913870368</v>
+        <v>4.968062401840585</v>
       </c>
       <c r="J135" t="n">
-        <v>-6</v>
+        <v>-13</v>
       </c>
       <c r="K135" t="n">
-        <v>-4</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -6817,30 +6817,30 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>IT0005416281</t>
+          <t>IT0005203424</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>6.050000190734863</v>
+        <v>42</v>
       </c>
       <c r="I136" t="n">
-        <v>4.958677529621045</v>
+        <v>2.619047619047619</v>
       </c>
       <c r="J136" t="n">
-        <v>-6</v>
+        <v>-13</v>
       </c>
       <c r="K136" t="n">
-        <v>-4</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.2</v>
+        <v>0.75</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -6849,45 +6849,45 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Straordinario</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>IT0005037905</t>
+          <t>IT0005252736</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>11.5</v>
+        <v>16.89999961853027</v>
       </c>
       <c r="I137" t="n">
-        <v>1.739130434782609</v>
+        <v>4.437869922657575</v>
       </c>
       <c r="J137" t="n">
-        <v>-6</v>
+        <v>-13</v>
       </c>
       <c r="K137" t="n">
-        <v>-4</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.06</v>
+        <v>0.43</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -6896,45 +6896,45 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>IT0005337818</t>
+          <t>IT0003203947</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>9.399999618530273</v>
+        <v>10.39999961853027</v>
       </c>
       <c r="I138" t="n">
-        <v>0.6382978982437579</v>
+        <v>4.134615536272179</v>
       </c>
       <c r="J138" t="n">
-        <v>-6</v>
+        <v>-13</v>
       </c>
       <c r="K138" t="n">
-        <v>-4</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -6943,12 +6943,12 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6958,30 +6958,30 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>IT0005075764</t>
+          <t>IT0005322612</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>18.81999969482422</v>
+        <v>4.050000190734863</v>
       </c>
       <c r="I139" t="n">
-        <v>2.656748183356812</v>
+        <v>3.703703529277682</v>
       </c>
       <c r="J139" t="n">
-        <v>-6</v>
+        <v>-13</v>
       </c>
       <c r="K139" t="n">
-        <v>-4</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.06</v>
+        <v>0.197169</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -7005,30 +7005,30 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>IT0004376858</t>
+          <t>IT0005455875</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>2.180000066757202</v>
+        <v>11.77999973297119</v>
       </c>
       <c r="I140" t="n">
-        <v>2.752293493699352</v>
+        <v>1.673760649146206</v>
       </c>
       <c r="J140" t="n">
-        <v>-6</v>
+        <v>-13</v>
       </c>
       <c r="K140" t="n">
-        <v>-4</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -7037,12 +7037,12 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -7052,30 +7052,30 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>IT0005138703</t>
+          <t>IT0005253205</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>15.03999996185303</v>
+        <v>27.89999961853027</v>
       </c>
       <c r="I141" t="n">
-        <v>3.324468093538457</v>
+        <v>3.942652383656005</v>
       </c>
       <c r="J141" t="n">
-        <v>-6</v>
+        <v>-13</v>
       </c>
       <c r="K141" t="n">
-        <v>-4</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.1</v>
+        <v>0.47</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -7084,12 +7084,12 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -7099,30 +7099,30 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>IT0005430951</t>
+          <t>IT0005107492</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>3.779999971389771</v>
+        <v>66.40000152587891</v>
       </c>
       <c r="I142" t="n">
-        <v>2.645502665526042</v>
+        <v>0.7078313090351677</v>
       </c>
       <c r="J142" t="n">
-        <v>-6</v>
+        <v>-13</v>
       </c>
       <c r="K142" t="n">
-        <v>-4</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.11</v>
+        <v>1.2</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -7131,12 +7131,12 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -7146,30 +7146,30 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>IT0005339160</t>
+          <t>IT0005274094</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>3.700000047683716</v>
+        <v>89.90000152587891</v>
       </c>
       <c r="I143" t="n">
-        <v>2.972972934658812</v>
+        <v>1.334816440080442</v>
       </c>
       <c r="J143" t="n">
-        <v>-6</v>
+        <v>-13</v>
       </c>
       <c r="K143" t="n">
-        <v>-4</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.27</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -7193,30 +7193,30 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>IT0005545238</t>
+          <t>IT0005513202</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>8.899999618530273</v>
+        <v>23.20000076293945</v>
       </c>
       <c r="I144" t="n">
-        <v>0.9550562207106782</v>
+        <v>1.163793065176567</v>
       </c>
       <c r="J144" t="n">
-        <v>-6</v>
+        <v>-13</v>
       </c>
       <c r="K144" t="n">
-        <v>-4</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.095</v>
+        <v>0.38</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -7225,12 +7225,12 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -7240,30 +7240,30 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>IT0005466963</t>
+          <t>IT0001018362</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>4.949999809265137</v>
+        <v>10.35000038146973</v>
       </c>
       <c r="I145" t="n">
-        <v>1.919191993142792</v>
+        <v>3.671497449220761</v>
       </c>
       <c r="J145" t="n">
-        <v>-6</v>
+        <v>-13</v>
       </c>
       <c r="K145" t="n">
-        <v>-4</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.03</v>
+        <v>0.3</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -7272,12 +7272,12 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -7287,30 +7287,30 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>IT0005521551</t>
+          <t>IT0005440893</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>1.139999985694885</v>
+        <v>35.59999847412109</v>
       </c>
       <c r="I146" t="n">
-        <v>2.631578980390385</v>
+        <v>0.8426966653329513</v>
       </c>
       <c r="J146" t="n">
-        <v>-6</v>
+        <v>-13</v>
       </c>
       <c r="K146" t="n">
-        <v>-4</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.09</v>
+        <v>0.007</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -7319,12 +7319,12 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -7334,30 +7334,30 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>IT0005246142</t>
+          <t>IT0001073045</t>
         </is>
       </c>
       <c r="H147" t="n">
-        <v>7.849999904632568</v>
+        <v>0.1666000038385391</v>
       </c>
       <c r="I147" t="n">
-        <v>1.14649682921509</v>
+        <v>4.201680575460292</v>
       </c>
       <c r="J147" t="n">
-        <v>-6</v>
+        <v>-20</v>
       </c>
       <c r="K147" t="n">
-        <v>-4</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -7366,12 +7366,12 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -7381,30 +7381,30 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>IT0005532525</t>
+          <t>IT0001033700</t>
         </is>
       </c>
       <c r="H148" t="n">
-        <v>8.399999618530273</v>
+        <v>6.860000133514404</v>
       </c>
       <c r="I148" t="n">
-        <v>1.190476244539363</v>
+        <v>2.332361470640838</v>
       </c>
       <c r="J148" t="n">
-        <v>-6</v>
+        <v>-20</v>
       </c>
       <c r="K148" t="n">
-        <v>-4</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.22</v>
+        <v>0.065</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -7413,12 +7413,12 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -7428,30 +7428,30 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>IT0004171440</t>
+          <t>IT0003372205</t>
         </is>
       </c>
       <c r="H149" t="n">
-        <v>6.96999979019165</v>
+        <v>2.055000066757202</v>
       </c>
       <c r="I149" t="n">
-        <v>3.156384600033837</v>
+        <v>3.163016928878754</v>
       </c>
       <c r="J149" t="n">
-        <v>-6</v>
+        <v>-20</v>
       </c>
       <c r="K149" t="n">
-        <v>-4</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.61</v>
+        <v>0.25</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -7460,12 +7460,12 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -7475,30 +7475,30 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>IT0004720733</t>
+          <t>IT0003365613</t>
         </is>
       </c>
       <c r="H150" t="n">
-        <v>28.04999923706055</v>
+        <v>8.699999809265137</v>
       </c>
       <c r="I150" t="n">
-        <v>2.174688116190922</v>
+        <v>2.873563281389506</v>
       </c>
       <c r="J150" t="n">
-        <v>-13</v>
+        <v>-20</v>
       </c>
       <c r="K150" t="n">
-        <v>-11</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.15</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -7507,12 +7507,12 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -7522,30 +7522,30 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>IT0005386369</t>
+          <t>IT0005549255</t>
         </is>
       </c>
       <c r="H151" t="n">
-        <v>2.859999895095825</v>
+        <v>1.299999952316284</v>
       </c>
       <c r="I151" t="n">
-        <v>5.244755437131728</v>
+        <v>5.384615582121908</v>
       </c>
       <c r="J151" t="n">
-        <v>-13</v>
+        <v>-20</v>
       </c>
       <c r="K151" t="n">
-        <v>-11</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -7569,30 +7569,30 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>IT0001268561</t>
+          <t>IT0004998065</t>
         </is>
       </c>
       <c r="H152" t="n">
-        <v>11.10000038146973</v>
+        <v>7.239999771118164</v>
       </c>
       <c r="I152" t="n">
-        <v>6.306306089579743</v>
+        <v>6.906077566391673</v>
       </c>
       <c r="J152" t="n">
-        <v>-13</v>
+        <v>-27</v>
       </c>
       <c r="K152" t="n">
-        <v>-11</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5105</v>
+        <v>0.65</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -7601,12 +7601,12 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -7616,44 +7616,44 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>IT0001041000</t>
+          <t>IT0004776628</t>
         </is>
       </c>
       <c r="H153" t="n">
-        <v>8.649999618530273</v>
+        <v>19.1200008392334</v>
       </c>
       <c r="I153" t="n">
-        <v>5.901734364315953</v>
+        <v>3.399581440740466</v>
       </c>
       <c r="J153" t="n">
-        <v>-13</v>
+        <v>-27</v>
       </c>
       <c r="K153" t="n">
-        <v>-11</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.27</v>
+        <v>0.54</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>DOLLARI USA</t>
+          <t>EURO</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -7663,30 +7663,30 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>LU2592315662</t>
+          <t>IT0005218380</t>
         </is>
       </c>
       <c r="H154" t="n">
-        <v>8.340000152587891</v>
+        <v>13.09500026702881</v>
       </c>
       <c r="I154" t="n">
-        <v>3.237410012711084</v>
+        <v>4.123711256116861</v>
       </c>
       <c r="J154" t="n">
-        <v>-13</v>
+        <v>-27</v>
       </c>
       <c r="K154" t="n">
-        <v>-11</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.35</v>
+        <v>0.1</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -7695,12 +7695,12 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -7710,30 +7710,30 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>IT0003850929</t>
+          <t>NL0015435975</t>
         </is>
       </c>
       <c r="H155" t="n">
-        <v>7.045000076293945</v>
+        <v>5.401999950408936</v>
       </c>
       <c r="I155" t="n">
-        <v>4.968062401840585</v>
+        <v>1.851166251721826</v>
       </c>
       <c r="J155" t="n">
-        <v>-13</v>
+        <v>-27</v>
       </c>
       <c r="K155" t="n">
-        <v>-11</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>1.1</v>
+        <v>0.16</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -7742,12 +7742,12 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -7757,30 +7757,30 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>IT0005203424</t>
+          <t>IT0005215329</t>
         </is>
       </c>
       <c r="H156" t="n">
-        <v>42</v>
+        <v>8.119999885559082</v>
       </c>
       <c r="I156" t="n">
-        <v>2.619047619047619</v>
+        <v>1.97044337752455</v>
       </c>
       <c r="J156" t="n">
-        <v>-13</v>
+        <v>-27</v>
       </c>
       <c r="K156" t="n">
-        <v>-11</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.75</v>
+        <v>3.615</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -7789,45 +7789,45 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Straordinario</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>IT0005252736</t>
+          <t>NL0011585146</t>
         </is>
       </c>
       <c r="H157" t="n">
-        <v>16.89999961853027</v>
+        <v>279.3999938964844</v>
       </c>
       <c r="I157" t="n">
-        <v>4.437869922657575</v>
+        <v>1.293843979588393</v>
       </c>
       <c r="J157" t="n">
-        <v>-13</v>
+        <v>-27</v>
       </c>
       <c r="K157" t="n">
-        <v>-11</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.43</v>
+        <v>1.36</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -7836,12 +7836,12 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -7851,30 +7851,30 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>IT0003203947</t>
+          <t>IT0005144784</t>
         </is>
       </c>
       <c r="H158" t="n">
-        <v>10.39999961853027</v>
+        <v>28.20000076293945</v>
       </c>
       <c r="I158" t="n">
-        <v>4.134615536272179</v>
+        <v>4.822694904984957</v>
       </c>
       <c r="J158" t="n">
-        <v>-13</v>
+        <v>-27</v>
       </c>
       <c r="K158" t="n">
-        <v>-11</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.15</v>
+        <v>5.8216</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -7883,45 +7883,45 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Straordinario</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>IT0005322612</t>
+          <t>NL0015000LU4</t>
         </is>
       </c>
       <c r="H159" t="n">
-        <v>4.050000190734863</v>
+        <v>13.93000030517578</v>
       </c>
       <c r="I159" t="n">
-        <v>3.703703529277682</v>
+        <v>41.79181530840992</v>
       </c>
       <c r="J159" t="n">
-        <v>-13</v>
+        <v>-27</v>
       </c>
       <c r="K159" t="n">
-        <v>-11</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.197169</v>
+        <v>0.585</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -7930,12 +7930,12 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -7945,30 +7945,30 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>IT0005455875</t>
+          <t>IT0004931058</t>
         </is>
       </c>
       <c r="H160" t="n">
-        <v>11.77999973297119</v>
+        <v>14.5</v>
       </c>
       <c r="I160" t="n">
-        <v>1.673760649146206</v>
+        <v>4.03448275862069</v>
       </c>
       <c r="J160" t="n">
-        <v>-13</v>
+        <v>-27</v>
       </c>
       <c r="K160" t="n">
-        <v>-11</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>1.1</v>
+        <v>0.63</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -7977,12 +7977,12 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -7992,30 +7992,30 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>IT0005253205</t>
+          <t>IT0000062957</t>
         </is>
       </c>
       <c r="H161" t="n">
-        <v>27.89999961853027</v>
+        <v>20.46999931335449</v>
       </c>
       <c r="I161" t="n">
-        <v>3.942652383656005</v>
+        <v>3.077674749060652</v>
       </c>
       <c r="J161" t="n">
-        <v>-13</v>
+        <v>-27</v>
       </c>
       <c r="K161" t="n">
-        <v>-11</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.47</v>
+        <v>0.9</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -8024,12 +8024,12 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -8039,30 +8039,30 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>IT0005107492</t>
+          <t>IT0004176001</t>
         </is>
       </c>
       <c r="H162" t="n">
-        <v>66.40000152587891</v>
+        <v>153.1499938964844</v>
       </c>
       <c r="I162" t="n">
-        <v>0.7078313090351677</v>
+        <v>0.587659181108632</v>
       </c>
       <c r="J162" t="n">
-        <v>-13</v>
+        <v>-27</v>
       </c>
       <c r="K162" t="n">
-        <v>-11</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>1.2</v>
+        <v>1.7208</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -8071,12 +8071,12 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -8086,959 +8086,19 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>IT0005274094</t>
+          <t>IT0005239360</t>
         </is>
       </c>
       <c r="H163" t="n">
-        <v>89.90000152587891</v>
+        <v>71.26000213623047</v>
       </c>
       <c r="I163" t="n">
-        <v>1.334816440080442</v>
+        <v>2.414818900384371</v>
       </c>
       <c r="J163" t="n">
-        <v>-13</v>
+        <v>-27</v>
       </c>
       <c r="K163" t="n">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>REVO Insurance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B164" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>IT0005513202</t>
-        </is>
-      </c>
-      <c r="H164" t="n">
-        <v>23.20000076293945</v>
-      </c>
-      <c r="I164" t="n">
-        <v>1.163793065176567</v>
-      </c>
-      <c r="J164" t="n">
-        <v>-13</v>
-      </c>
-      <c r="K164" t="n">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>VALSOIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B165" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>IT0001018362</t>
-        </is>
-      </c>
-      <c r="H165" t="n">
-        <v>10.35000038146973</v>
-      </c>
-      <c r="I165" t="n">
-        <v>3.671497449220761</v>
-      </c>
-      <c r="J165" t="n">
-        <v>-13</v>
-      </c>
-      <c r="K165" t="n">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>WIIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B166" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>IT0005440893</t>
-        </is>
-      </c>
-      <c r="H166" t="n">
-        <v>35.59999847412109</v>
-      </c>
-      <c r="I166" t="n">
-        <v>0.8426966653329513</v>
-      </c>
-      <c r="J166" t="n">
-        <v>-13</v>
-      </c>
-      <c r="K166" t="n">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Banca Profilo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B167" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>IT0001073045</t>
-        </is>
-      </c>
-      <c r="H167" t="n">
-        <v>0.1666000038385391</v>
-      </c>
-      <c r="I167" t="n">
-        <v>4.201680575460292</v>
-      </c>
-      <c r="J167" t="n">
-        <v>-20</v>
-      </c>
-      <c r="K167" t="n">
-        <v>-18</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Basic Net S.p.A.</t>
-        </is>
-      </c>
-      <c r="B168" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>IT0001033700</t>
-        </is>
-      </c>
-      <c r="H168" t="n">
-        <v>6.860000133514404</v>
-      </c>
-      <c r="I168" t="n">
-        <v>2.332361470640838</v>
-      </c>
-      <c r="J168" t="n">
-        <v>-20</v>
-      </c>
-      <c r="K168" t="n">
-        <v>-18</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>EDISON S.p.A.</t>
-        </is>
-      </c>
-      <c r="B169" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>IT0003372205</t>
-        </is>
-      </c>
-      <c r="H169" t="n">
-        <v>2.055000066757202</v>
-      </c>
-      <c r="I169" t="n">
-        <v>3.163016928878754</v>
-      </c>
-      <c r="J169" t="n">
-        <v>-20</v>
-      </c>
-      <c r="K169" t="n">
-        <v>-18</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Fiera Milano S.p.A</t>
-        </is>
-      </c>
-      <c r="B170" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>IT0003365613</t>
-        </is>
-      </c>
-      <c r="H170" t="n">
-        <v>8.699999809265137</v>
-      </c>
-      <c r="I170" t="n">
-        <v>2.873563281389506</v>
-      </c>
-      <c r="J170" t="n">
-        <v>-20</v>
-      </c>
-      <c r="K170" t="n">
-        <v>-18</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
-        </is>
-      </c>
-      <c r="B171" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>IT0005549255</t>
-        </is>
-      </c>
-      <c r="H171" t="n">
-        <v>1.299999952316284</v>
-      </c>
-      <c r="I171" t="n">
-        <v>5.384615582121908</v>
-      </c>
-      <c r="J171" t="n">
-        <v>-20</v>
-      </c>
-      <c r="K171" t="n">
-        <v>-18</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Anima Holding S.p.A.</t>
-        </is>
-      </c>
-      <c r="B172" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>IT0004998065</t>
-        </is>
-      </c>
-      <c r="H172" t="n">
-        <v>7.239999771118164</v>
-      </c>
-      <c r="I172" t="n">
-        <v>6.906077566391673</v>
-      </c>
-      <c r="J172" t="n">
-        <v>-27</v>
-      </c>
-      <c r="K172" t="n">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B173" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>IT0004776628</t>
-        </is>
-      </c>
-      <c r="H173" t="n">
-        <v>19.1200008392334</v>
-      </c>
-      <c r="I173" t="n">
-        <v>3.399581440740466</v>
-      </c>
-      <c r="J173" t="n">
-        <v>-27</v>
-      </c>
-      <c r="K173" t="n">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Banco BPM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B174" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>IT0005218380</t>
-        </is>
-      </c>
-      <c r="H174" t="n">
-        <v>13.09500026702881</v>
-      </c>
-      <c r="I174" t="n">
-        <v>4.123711256116861</v>
-      </c>
-      <c r="J174" t="n">
-        <v>-27</v>
-      </c>
-      <c r="K174" t="n">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Davide Campari-Milano N.V.</t>
-        </is>
-      </c>
-      <c r="B175" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>NL0015435975</t>
-        </is>
-      </c>
-      <c r="H175" t="n">
-        <v>5.401999950408936</v>
-      </c>
-      <c r="I175" t="n">
-        <v>1.851166251721826</v>
-      </c>
-      <c r="J175" t="n">
-        <v>-27</v>
-      </c>
-      <c r="K175" t="n">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B176" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>IT0005215329</t>
-        </is>
-      </c>
-      <c r="H176" t="n">
-        <v>8.119999885559082</v>
-      </c>
-      <c r="I176" t="n">
-        <v>1.97044337752455</v>
-      </c>
-      <c r="J176" t="n">
-        <v>-27</v>
-      </c>
-      <c r="K176" t="n">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Ferrari N.V.</t>
-        </is>
-      </c>
-      <c r="B177" t="n">
-        <v>3.615</v>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>NL0011585146</t>
-        </is>
-      </c>
-      <c r="H177" t="n">
-        <v>279.3999938964844</v>
-      </c>
-      <c r="I177" t="n">
-        <v>1.293843979588393</v>
-      </c>
-      <c r="J177" t="n">
-        <v>-27</v>
-      </c>
-      <c r="K177" t="n">
-        <v>-12</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Generalfinance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B178" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>IT0005144784</t>
-        </is>
-      </c>
-      <c r="H178" t="n">
-        <v>28.20000076293945</v>
-      </c>
-      <c r="I178" t="n">
-        <v>4.822694904984957</v>
-      </c>
-      <c r="J178" t="n">
-        <v>-27</v>
-      </c>
-      <c r="K178" t="n">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Iveco Group N.V.</t>
-        </is>
-      </c>
-      <c r="B179" t="n">
-        <v>5.8216</v>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>Straordinario</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>NL0015000LU4</t>
-        </is>
-      </c>
-      <c r="H179" t="n">
-        <v>13.93000030517578</v>
-      </c>
-      <c r="I179" t="n">
-        <v>41.79181530840992</v>
-      </c>
-      <c r="J179" t="n">
-        <v>-27</v>
-      </c>
-      <c r="K179" t="n">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>MAIRE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B180" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>IT0004931058</t>
-        </is>
-      </c>
-      <c r="H180" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="I180" t="n">
-        <v>4.03448275862069</v>
-      </c>
-      <c r="J180" t="n">
-        <v>-27</v>
-      </c>
-      <c r="K180" t="n">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
-        </is>
-      </c>
-      <c r="B181" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>IT0000062957</t>
-        </is>
-      </c>
-      <c r="H181" t="n">
-        <v>20.46999931335449</v>
-      </c>
-      <c r="I181" t="n">
-        <v>3.077674749060652</v>
-      </c>
-      <c r="J181" t="n">
-        <v>-27</v>
-      </c>
-      <c r="K181" t="n">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Prysmian S.p.A.</t>
-        </is>
-      </c>
-      <c r="B182" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>IT0004176001</t>
-        </is>
-      </c>
-      <c r="H182" t="n">
-        <v>153.1499938964844</v>
-      </c>
-      <c r="I182" t="n">
-        <v>0.587659181108632</v>
-      </c>
-      <c r="J182" t="n">
-        <v>-27</v>
-      </c>
-      <c r="K182" t="n">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Unicredit S.p.A.</t>
-        </is>
-      </c>
-      <c r="B183" t="n">
-        <v>1.7208</v>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>IT0005239360</t>
-        </is>
-      </c>
-      <c r="H183" t="n">
-        <v>71.26000213623047</v>
-      </c>
-      <c r="I183" t="n">
-        <v>2.414818900384371</v>
-      </c>
-      <c r="J183" t="n">
-        <v>-27</v>
-      </c>
-      <c r="K183" t="n">
         <v>-25</v>
       </c>
     </row>
@@ -10946,7 +10006,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Abitare In S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10956,7 +10016,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -10980,7 +10040,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Abitare In S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10990,7 +10050,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -11014,7 +10074,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Adventure S.p.A.</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11048,7 +10108,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>Adventure S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11099,7 +10159,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11109,14 +10169,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11126,7 +10186,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -11143,14 +10203,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11239,78 +10299,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BFF Bank S.P.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Gas Plus S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>